--- a/assets/constructions/examples/ctd_mis_disk.xlsx
+++ b/assets/constructions/examples/ctd_mis_disk.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,59 +584,75 @@
           <t>multiplatform</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N331.52-203T51MM</t>
+          <t>MT390-080S27N04SN12-11.5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>СКИФ-М</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CoroMillⓇ 331 adjustable double half side and face disc milling cutter</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>30.201</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.203</v>
-      </c>
+          <t>MT390-S...N...SN12-11.5</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>27.203</v>
+        <v>11.5</v>
       </c>
       <c r="G2" t="n">
-        <v>203.2</v>
+        <v>80</v>
       </c>
       <c r="H2" t="n">
-        <v>50.8</v>
+        <v>27</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>29.197</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N2" t="n">
+        <v>10500</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P2" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q2" t="n">
         <v>12</v>
       </c>
-      <c r="M2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N2" t="n">
-        <v>9600</v>
-      </c>
-      <c r="O2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="P2" t="n">
-        <v>66.497</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>E</t>
@@ -644,17 +660,17 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CoroMill 331 -size 11 (N/L331.1A-11RE0.20-1.54)</t>
+          <t>SNEC1264...</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ISO_240_2KEYDRIVES:50.8</t>
+          <t>ISO_11529:FDA01-27</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>COR_331.1A-11H</t>
+          <t>SKIF_SN1264H</t>
         </is>
       </c>
       <c r="V2" t="n">
@@ -663,7 +679,9 @@
       <c r="W2" t="n">
         <v>1</v>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>4</v>
+      </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
@@ -674,60 +692,70 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
+          <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>COR_331.1A-11_H</t>
-        </is>
-      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSGF90-D80-27-12-11-8</t>
+          <t>MT390K-160S40N07SO12-1619</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>СКИФ-М</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DSGF90</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>MT390K-S...N...SO12</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3" t="n">
+        <v>16</v>
+      </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="H3" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>11</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M3" t="n">
-        <v>8</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="N3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="P3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>16</v>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
           <t>E</t>
@@ -735,17 +763,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>SCMT09T3</t>
+          <t>SOMT120408..N...</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ISO_11529:FDA01-27</t>
+          <t>ISO_11529:FDA01-40</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>ISO_SC09T3H</t>
+          <t>SKIF_SO1204H</t>
         </is>
       </c>
       <c r="V3" t="n">
@@ -767,36 +795,42 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
+          <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>SC09T3H</t>
-        </is>
-      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MT390-125S40N05SD08-12</t>
+          <t>N331.32-125S40CM06.00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MT390-S...N...SD08-12</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>CoroMillⓇ 331 adjustable full side and face disc milling cutter</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
         <v>125</v>
@@ -806,25 +840,25 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>10</v>
+      </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
         <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>11000</v>
+        <v>15100</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7</v>
+        <v>0.41</v>
       </c>
       <c r="P4" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>12</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>E</t>
@@ -832,17 +866,17 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>SDMT08T308ER + SDMT08T308EL</t>
+          <t>CoroMill 331 -size 04 (N/R331.1A-04RE0.20-1.54)</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ISO_11529:FDA01-40</t>
+          <t>ISO_240_2KEYDRIVES:40</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SKIF_SD08T3RH + SKIF_SD08T3LH</t>
+          <t>COR_331.1A-04H</t>
         </is>
       </c>
       <c r="V4" t="n">
@@ -851,9 +885,7 @@
       <c r="W4" t="n">
         <v>1</v>
       </c>
-      <c r="X4" t="n">
-        <v>4</v>
-      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
@@ -864,78 +896,90 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
+          <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>COR_331.1A-04_H</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MT390K-200S50R20AX14</t>
+          <t>WDC-160-18B-40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MT390K-S...R...AX14</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E5" t="n">
+        <v>18</v>
+      </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>20</v>
+      </c>
       <c r="L5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>20</v>
-      </c>
-      <c r="N5" t="n">
-        <v>6000</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P5" t="n">
-        <v>64</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>20</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>AXGT1405..ER</t>
+          <t>SPMT110408</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ISO_11529:FDA01-50</t>
+          <t>ISO_11529:FDA01-40</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SKIF_AX1405RH</t>
+          <t>DER_SP0904H</t>
         </is>
       </c>
       <c r="V5" t="n">
@@ -945,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -954,67 +998,87 @@
         <v>0</v>
       </c>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+      <c r="AB5" t="b">
+        <v>0</v>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
+          <t>2019 / DEREK</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>SP0904_H</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>427.36</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>35032.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MT390K-250S60N08SO12-1922</t>
+          <t>N331.32C-080S27EM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MT390K-S...N...SO12</t>
+          <t>CoroMillⓇ 331 adjustable full side and face disc milling cutter</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>13</v>
+      </c>
       <c r="L6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="N6" t="n">
-        <v>5500</v>
+        <v>18100</v>
       </c>
       <c r="O6" t="n">
-        <v>5.5</v>
+        <v>0.229</v>
       </c>
       <c r="P6" t="n">
-        <v>83</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>19</v>
-      </c>
+        <v>19.5</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>E</t>
@@ -1022,17 +1086,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>SOMT120408..N...</t>
+          <t>CoroMill 331 -size 08 (N/R331.1A-08RE0.20-1.54)</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ISO_11529:FDA01-60</t>
+          <t>ISO_11529:FDA01-27</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SKIF_SO1204H</t>
+          <t>COR_331.1A-08H</t>
         </is>
       </c>
       <c r="V6" t="n">
@@ -1041,24 +1105,32 @@
       <c r="W6" t="n">
         <v>1</v>
       </c>
-      <c r="X6" t="n">
-        <v>4</v>
-      </c>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
+          <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>COR_331.1A-08_H</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
